--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -1,45 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NoguchiTakuya\Documents\Claude\projects\テンプレート作成\03_設計\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A8B1AD5-631D-459D-BF28-7F489CC436FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="6570" yWindow="-11835" windowWidth="17280" windowHeight="10680" activeTab="3" xr2:uid="{900B833C-72D3-4F3F-95D9-ED43B39E1931}"/>
+    <workbookView xWindow="6570" yWindow="-11835" windowWidth="17280" windowHeight="10680" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="取引先" sheetId="1" r:id="rId1"/>
-    <sheet name="取引先責任者" sheetId="2" r:id="rId2"/>
-    <sheet name="商談" sheetId="3" r:id="rId3"/>
-    <sheet name="リード" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="取引先" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="取引先責任者" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="商談" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="164">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -264,6 +242,18 @@
   </si>
   <si>
     <t>カスタム項目、活動履歴から自動更新</t>
+  </si>
+  <si>
+    <t>Test__c</t>
+  </si>
+  <si>
+    <t>テスト項目</t>
+  </si>
+  <si>
+    <t>テスト項目（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目、Issue #1</t>
   </si>
   <si>
     <t>項目定義書　－ 取引先責任者オブジェクト（Contact）</t>
@@ -524,49 +514,49 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FFFFFFFF"/>
+      <family val="3"/>
+      <scheme val="minor"/>
       <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
-      <family val="3"/>
+    </font>
+    <font>
       <charset val="128"/>
+      <color theme="1"/>
+      <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FFFFFFFF"/>
+      <family val="3"/>
+      <scheme val="minor"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <charset val="128"/>
+      <color rgb="FFC00000"/>
+      <family val="3"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
       <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -643,6 +633,19 @@
       <left style="thin">
         <color rgb="FFD2D2D2"/>
       </left>
+      <right style="thin">
+        <color rgb="FFD2D2D2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD2D2D2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD2D2D2"/>
+      </left>
       <right/>
       <top style="thin">
         <color rgb="FFD2D2D2"/>
@@ -667,110 +670,93 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD2D2D2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD2D2D2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD2D2D2"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1101,9 +1087,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858D6FC1-04B4-46E2-8A1F-4C11D190D841}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -1114,7 +1100,7 @@
     <col min="9" max="9" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1113,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1138,7 +1124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1167,7 +1153,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
@@ -1183,337 +1169,361 @@
       <c r="E4" s="4">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>255</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>40</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="19" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="9" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19" t="s">
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>40</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19" t="s">
+      <c r="F12" s="11"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="7">
         <v>255</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="12" t="s">
+      <c r="F13" s="13"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
+      <c r="E14" s="10"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="12" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="9" t="s">
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="7">
         <v>32000</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="20" t="s">
+      <c r="F15" s="13"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="20" t="s">
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I16" s="25" t="s">
+      <c r="H16" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="21" t="s">
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E17" s="21"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="22" t="s">
+      <c r="E17" s="17"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="19" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="17">
+        <v>255</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1583F6D6-C25C-4EB8-9E2B-454A26C07366}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -1524,9 +1534,9 @@
     <col min="9" max="9" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1537,7 +1547,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1548,7 +1558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1577,12 +1587,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -1593,258 +1603,257 @@
       <c r="E4" s="4">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="10">
         <v>80</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10" t="s">
+      <c r="F6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E7" s="7">
+        <v>40</v>
+      </c>
+      <c r="F7" s="13"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="10">
+        <v>128</v>
+      </c>
+      <c r="F8" s="11"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7">
         <v>80</v>
       </c>
-      <c r="F6" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
+      <c r="F9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="10">
+        <v>80</v>
+      </c>
+      <c r="F10" s="11"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="7">
+        <v>40</v>
+      </c>
+      <c r="F11" s="13"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="10">
+        <v>40</v>
+      </c>
+      <c r="F12" s="11"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="9">
-        <v>40</v>
-      </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="12">
-        <v>128</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="9">
-        <v>80</v>
-      </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="12">
-        <v>80</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="9">
-        <v>40</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="12">
-        <v>40</v>
-      </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="14"/>
+      <c r="I14" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB16BB33-C7E1-4DB9-B3F1-856C59E6577F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I15"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -1855,9 +1864,9 @@
     <col min="9" max="9" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1868,7 +1877,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1879,7 +1888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1908,12 +1917,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -1924,289 +1933,288 @@
       <c r="E4" s="4">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="B5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>120</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="I5" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="26" t="s">
+      <c r="C6" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="I7" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="26" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="B10" s="10" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="I10" s="12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="C12" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="10">
         <v>32000</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
+      <c r="F12" s="11"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D14" s="20" t="s">
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="14">
         <v>255</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="25" t="s">
+      <c r="F14" s="15"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="16" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="D15" s="21" t="s">
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>137</v>
+      <c r="E15" s="17"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE090E5C-8ADA-443C-821A-ABCAB7449EBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
     <col min="4" max="4" width="20.69921875" customWidth="1"/>
@@ -2217,9 +2225,9 @@
     <col min="9" max="9" width="35.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2230,7 +2238,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2241,7 +2249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -2270,12 +2278,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2286,300 +2294,299 @@
       <c r="E4" s="4">
         <v>18</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="I4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="7">
         <v>80</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="17"/>
-    </row>
-    <row r="6" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>40</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="19"/>
-    </row>
-    <row r="7" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="12"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="7">
         <v>255</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9" t="s">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>128</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="F8" s="11"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="7">
         <v>80</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="12" t="s">
+      <c r="F9" s="13"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>40</v>
       </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="19"/>
-    </row>
-    <row r="11" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="F10" s="11"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="12"/>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="G11" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="19"/>
-    </row>
-    <row r="13" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="E12" s="10"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="12" t="s">
+      <c r="E13" s="7"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="C14" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="10">
         <v>32000</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="9" t="s">
+      <c r="F14" s="11"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I15" s="17"/>
-    </row>
-    <row r="16" spans="1:9" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>159</v>
+      <c r="I16" s="26" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -11,13 +11,14 @@
     <sheet sheetId="2" name="取引先責任者" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="商談" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="ユーザー" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="170">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -85,7 +86,7 @@
     <t>○</t>
   </si>
   <si>
-    <t>正式会社名を入力</t>
+    <t>正式会社名を入力。個人のお客様は「個人のお客様」取引先1件にまとめる</t>
   </si>
   <si>
     <t>AccountNumber</t>
@@ -509,6 +510,24 @@
   </si>
   <si>
     <t>商談化時に自動でTrue</t>
+  </si>
+  <si>
+    <t>項目定義書　－ ユーザーオブジェクト（User）</t>
+  </si>
+  <si>
+    <t>Store__c</t>
+  </si>
+  <si>
+    <t>所属店舗</t>
+  </si>
+  <si>
+    <t>所属店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ/本社</t>
+  </si>
+  <si>
+    <t>カスタム項目。グローバル選択リスト「店舗」(Store)を使用。ケース・商談の店舗の初期値になる</t>
   </si>
 </sst>
 </file>
@@ -1113,7 +1132,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2589,4 +2608,105 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -12,13 +12,14 @@
     <sheet sheetId="3" name="商談" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="ユーザー" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="ケース" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="201">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -528,6 +529,99 @@
   </si>
   <si>
     <t>カスタム項目。グローバル選択リスト「店舗」(Store)を使用。ケース・商談の店舗の初期値になる</t>
+  </si>
+  <si>
+    <t>項目定義書　－ ケースオブジェクト（Case）</t>
+  </si>
+  <si>
+    <t>CaseNumber</t>
+  </si>
+  <si>
+    <t>ケース番号</t>
+  </si>
+  <si>
+    <t>Salesforce標準</t>
+  </si>
+  <si>
+    <t>取引先責任者</t>
+  </si>
+  <si>
+    <t>お客様（会員）</t>
+  </si>
+  <si>
+    <t>参照（Contact）</t>
+  </si>
+  <si>
+    <t>問い合わせたお客様</t>
+  </si>
+  <si>
+    <t>お客様の取引先から自動設定</t>
+  </si>
+  <si>
+    <t>店舗</t>
+  </si>
+  <si>
+    <t>店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。グローバル選択リスト「店舗」。空欄なら作成者の所属店舗をフロー「ケース：店舗の初期値」で設定</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>問い合わせ種別</t>
+  </si>
+  <si>
+    <t>商品について/ギフト/定期便/法人のお取引/クレーム/その他</t>
+  </si>
+  <si>
+    <t>標準選択リストに値を追加（既存の値は残している）</t>
+  </si>
+  <si>
+    <t>Origin</t>
+  </si>
+  <si>
+    <t>発生源</t>
+  </si>
+  <si>
+    <t>受付方法</t>
+  </si>
+  <si>
+    <t>店頭/電話/電子メール/Web</t>
+  </si>
+  <si>
+    <t>標準選択リストに「店頭」を追加</t>
+  </si>
+  <si>
+    <t>状況</t>
+  </si>
+  <si>
+    <t>新規/対応中/エスカレーション/完了 など</t>
+  </si>
+  <si>
+    <t>Salesforce標準値</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>件名</t>
+  </si>
+  <si>
+    <t>問い合わせ内容</t>
+  </si>
+  <si>
+    <t>所有者</t>
+  </si>
+  <si>
+    <t>担当者</t>
+  </si>
+  <si>
+    <t>参照（ユーザー/キュー）</t>
+  </si>
+  <si>
+    <t>未割り当ては「本社カスタマーサクセス」キュー</t>
   </si>
 </sst>
 </file>
@@ -2637,7 +2731,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2700,6 +2794,328 @@
       </c>
       <c r="I4" s="9" t="s">
         <v>169</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="7">
+        <v>30</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="7">
+        <v>255</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="7">
+        <v>32000</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="214">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -363,7 +363,7 @@
     <t>ヒアリング/提案/見積/交渉/受注/失注</t>
   </si>
   <si>
-    <t>受注確度に連動</t>
+    <t>標準選択リストに値を追加。確度：ヒアリング10%・提案50%・見積60%・交渉80%・受注100%・失注0%（既存の値は残している）</t>
   </si>
   <si>
     <t>CloseDate</t>
@@ -447,6 +447,60 @@
     <t>カスタム項目、失注時は必須</t>
   </si>
   <si>
+    <t>Store__c</t>
+  </si>
+  <si>
+    <t>店舗</t>
+  </si>
+  <si>
+    <t>店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ/本社</t>
+  </si>
+  <si>
+    <t>カスタム項目。グローバル選択リスト「店舗」。空欄なら作成者の所属店舗をフロー「商談：店舗の初期値」で設定</t>
+  </si>
+  <si>
+    <t>MonthlyAmount__c</t>
+  </si>
+  <si>
+    <t>月額見込み</t>
+  </si>
+  <si>
+    <t>月額見込み（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。オフィス定期便・業務用卸の1か月あたりの見込み金額（税抜）</t>
+  </si>
+  <si>
+    <t>商談 種別</t>
+  </si>
+  <si>
+    <t>商談種別</t>
+  </si>
+  <si>
+    <t>オフィス定期便/業務用卸</t>
+  </si>
+  <si>
+    <t>標準選択リストに値を追加（既存の値は残している）</t>
+  </si>
+  <si>
+    <t>CampaignId</t>
+  </si>
+  <si>
+    <t>主キャンペーン</t>
+  </si>
+  <si>
+    <t>キャンペーン</t>
+  </si>
+  <si>
+    <t>参照（Campaign）</t>
+  </si>
+  <si>
+    <t>キャンペーン効果（法人の受注額）の集計に使う</t>
+  </si>
+  <si>
     <t>項目定義書　－ リードオブジェクト（Lead）</t>
   </si>
   <si>
@@ -516,18 +570,12 @@
     <t>項目定義書　－ ユーザーオブジェクト（User）</t>
   </si>
   <si>
-    <t>Store__c</t>
-  </si>
-  <si>
     <t>所属店舗</t>
   </si>
   <si>
     <t>所属店舗（カスタム）</t>
   </si>
   <si>
-    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ/本社</t>
-  </si>
-  <si>
     <t>カスタム項目。グローバル選択リスト「店舗」(Store)を使用。ケース・商談の店舗の初期値になる</t>
   </si>
   <si>
@@ -558,12 +606,6 @@
     <t>お客様の取引先から自動設定</t>
   </si>
   <si>
-    <t>店舗</t>
-  </si>
-  <si>
-    <t>店舗（カスタム）</t>
-  </si>
-  <si>
     <t>カスタム項目。グローバル選択リスト「店舗」。空欄なら作成者の所属店舗をフロー「ケース：店舗の初期値」で設定</t>
   </si>
   <si>
@@ -574,9 +616,6 @@
   </si>
   <si>
     <t>商品について/ギフト/定期便/法人のお取引/クレーム/その他</t>
-  </si>
-  <si>
-    <t>標準選択リストに値を追加（既存の値は残している）</t>
   </si>
   <si>
     <t>Origin</t>
@@ -1226,7 +1265,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1965,7 +2004,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2314,6 +2353,102 @@
       </c>
       <c r="I15" s="19" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2340,7 +2475,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2393,10 +2528,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2466,13 +2601,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2560,13 +2695,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2576,7 +2711,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -2591,7 +2726,7 @@
         <v>128</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -2599,7 +2734,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -2608,13 +2743,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -2622,7 +2757,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -2637,7 +2772,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -2657,7 +2792,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -2675,16 +2810,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -2693,7 +2828,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2720,7 +2855,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2773,13 +2908,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>29</v>
@@ -2787,13 +2922,13 @@
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
       <c r="G4" s="7" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2821,7 +2956,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2832,7 +2967,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2874,13 +3009,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>82</v>
@@ -2894,7 +3029,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2902,13 +3037,13 @@
         <v>80</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -2917,7 +3052,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2940,18 +3075,18 @@
         <v>125</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2959,13 +3094,13 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2973,10 +3108,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -2984,24 +3119,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -3011,24 +3146,24 @@
         <v>21</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -3038,24 +3173,24 @@
         <v>21</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
@@ -3078,7 +3213,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>64</v>
@@ -3098,13 +3233,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="8" t="s">
@@ -3115,7 +3250,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -3123,6 +3258,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -13,13 +13,15 @@
     <sheet sheetId="4" name="リード" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="ユーザー" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="ケース" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="ポイントカード" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="ポイント履歴" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="274">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -336,6 +338,21 @@
     <t>取引先責任者オーナー</t>
   </si>
   <si>
+    <t>Store__c</t>
+  </si>
+  <si>
+    <t>よく行く店舗</t>
+  </si>
+  <si>
+    <t>よく行く店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ/本社</t>
+  </si>
+  <si>
+    <t>カスタム項目。グローバル選択リスト「店舗」。個人のお客様（会員）が主に利用する店舗</t>
+  </si>
+  <si>
     <t>項目定義書　－ 商談オブジェクト（Opportunity）</t>
   </si>
   <si>
@@ -447,18 +464,12 @@
     <t>カスタム項目、失注時は必須</t>
   </si>
   <si>
-    <t>Store__c</t>
-  </si>
-  <si>
     <t>店舗</t>
   </si>
   <si>
     <t>店舗（カスタム）</t>
   </si>
   <si>
-    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ/本社</t>
-  </si>
-  <si>
     <t>カスタム項目。グローバル選択リスト「店舗」。空欄なら作成者の所属店舗をフロー「商談：店舗の初期値」で設定</t>
   </si>
   <si>
@@ -661,6 +672,177 @@
   </si>
   <si>
     <t>未割り当ては「本社カスタマーサクセス」キュー</t>
+  </si>
+  <si>
+    <t>項目定義書　－ ポイントカードオブジェクト（PointCard__c）</t>
+  </si>
+  <si>
+    <t>カード管理番号</t>
+  </si>
+  <si>
+    <t>PC-000000 の形式</t>
+  </si>
+  <si>
+    <t>CardNumber__c</t>
+  </si>
+  <si>
+    <t>カード番号</t>
+  </si>
+  <si>
+    <t>一意・外部ID。バーコードで読み取る番号</t>
+  </si>
+  <si>
+    <t>Member__c</t>
+  </si>
+  <si>
+    <t>会員</t>
+  </si>
+  <si>
+    <t>取引先責任者への参照。カード再発行時は新しいカードに同じ会員を設定</t>
+  </si>
+  <si>
+    <t>MemberName__c</t>
+  </si>
+  <si>
+    <t>会員名</t>
+  </si>
+  <si>
+    <t>数式（テキスト）</t>
+  </si>
+  <si>
+    <t>会員の姓＋名</t>
+  </si>
+  <si>
+    <t>Status__c</t>
+  </si>
+  <si>
+    <t>状態</t>
+  </si>
+  <si>
+    <t>有効/停止</t>
+  </si>
+  <si>
+    <t>初期値：有効。停止中のカードは付与・利用できない</t>
+  </si>
+  <si>
+    <t>IssuedStore__c</t>
+  </si>
+  <si>
+    <t>発行店舗</t>
+  </si>
+  <si>
+    <t>グローバル選択リスト「店舗」</t>
+  </si>
+  <si>
+    <t>IssuedDate__c</t>
+  </si>
+  <si>
+    <t>発行日</t>
+  </si>
+  <si>
+    <t>初期値：今日</t>
+  </si>
+  <si>
+    <t>Balance__c</t>
+  </si>
+  <si>
+    <t>ポイント残高</t>
+  </si>
+  <si>
+    <t>積み上げ集計</t>
+  </si>
+  <si>
+    <t>ポイント履歴のポイント数の合計</t>
+  </si>
+  <si>
+    <t>項目定義書　－ ポイント履歴オブジェクト（PointTransaction__c）</t>
+  </si>
+  <si>
+    <t>履歴番号</t>
+  </si>
+  <si>
+    <t>PT-000000 の形式</t>
+  </si>
+  <si>
+    <t>PointCard__c</t>
+  </si>
+  <si>
+    <t>ポイントカード</t>
+  </si>
+  <si>
+    <t>主従関係（PointCard__c）</t>
+  </si>
+  <si>
+    <t>親：ポイントカード</t>
+  </si>
+  <si>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>付与/利用</t>
+  </si>
+  <si>
+    <t>初期値：付与</t>
+  </si>
+  <si>
+    <t>Points__c</t>
+  </si>
+  <si>
+    <t>ポイント数</t>
+  </si>
+  <si>
+    <t>付与はプラス、利用はマイナス（入力規則で確認）。画面フローでは購入金額100円につき1ポイント</t>
+  </si>
+  <si>
+    <t>PurchaseAmount__c</t>
+  </si>
+  <si>
+    <t>購入金額</t>
+  </si>
+  <si>
+    <t>税込。キャンペーン効果の集計に使う</t>
+  </si>
+  <si>
+    <t>グローバル選択リスト「店舗」。画面フローで空欄なら所属店舗</t>
+  </si>
+  <si>
+    <t>TransactionDate__c</t>
+  </si>
+  <si>
+    <t>利用日</t>
+  </si>
+  <si>
+    <t>（入力規則）NoNegativeBalance</t>
+  </si>
+  <si>
+    <t>残高不足</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>残高がマイナスになる利用はエラー</t>
+  </si>
+  <si>
+    <t>（入力規則）CardMustBeActive</t>
+  </si>
+  <si>
+    <t>停止カード</t>
+  </si>
+  <si>
+    <t>停止中のカードへの付与・利用はエラー</t>
+  </si>
+  <si>
+    <t>（入力規則）PointsSignByType</t>
+  </si>
+  <si>
+    <t>符号の確認</t>
+  </si>
+  <si>
+    <t>付与はプラス、利用はマイナス以外はエラー</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1447,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1674,7 +1856,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -1993,6 +2175,31 @@
         <v>9</v>
       </c>
       <c r="I14" s="23"/>
+    </row>
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>109</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2018,7 +2225,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2071,10 +2278,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2099,10 +2306,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2118,7 +2325,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2146,13 +2353,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2162,24 +2369,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2196,13 +2403,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2217,36 +2424,36 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2254,7 +2461,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -2269,7 +2476,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -2289,7 +2496,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -2307,13 +2514,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -2332,13 +2539,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -2346,24 +2553,24 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>29</v>
@@ -2371,24 +2578,24 @@
       <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="7" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>38</v>
@@ -2400,7 +2607,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2408,10 +2615,10 @@
         <v>27</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>29</v>
@@ -2419,27 +2626,27 @@
       <c r="E18" s="7"/>
       <c r="F18" s="8"/>
       <c r="G18" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
@@ -2448,7 +2655,7 @@
         <v>25</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2475,7 +2682,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2528,10 +2735,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2601,13 +2808,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2695,13 +2902,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2711,7 +2918,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -2720,13 +2927,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -2734,7 +2941,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -2743,13 +2950,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -2757,7 +2964,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -2772,7 +2979,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -2792,7 +2999,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -2810,16 +3017,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -2828,7 +3035,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -2855,7 +3062,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2908,13 +3115,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>29</v>
@@ -2922,13 +3129,13 @@
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
       <c r="G4" s="7" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2956,7 +3163,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3009,13 +3216,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>82</v>
@@ -3029,7 +3236,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3037,13 +3244,13 @@
         <v>80</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -3052,7 +3259,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3072,21 +3279,21 @@
       <c r="F6" s="8"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>142</v>
+        <v>105</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -3094,13 +3301,13 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3108,10 +3315,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -3119,24 +3326,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -3146,24 +3353,24 @@
         <v>21</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -3173,24 +3380,24 @@
         <v>21</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
@@ -3213,7 +3420,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>64</v>
@@ -3233,13 +3440,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="8" t="s">
@@ -3250,7 +3457,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -3260,4 +3467,605 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7">
+        <v>20</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="7">
+        <v>9</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -15,13 +15,14 @@
     <sheet sheetId="6" name="ケース" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="ポイントカード" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="ポイント履歴" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="キャンペーン" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="310">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -843,6 +844,114 @@
   </si>
   <si>
     <t>付与はプラス、利用はマイナス以外はエラー</t>
+  </si>
+  <si>
+    <t>Campaign__c</t>
+  </si>
+  <si>
+    <t>空欄なら、フロー「ポイント履歴：キャンペーンの自動設定」が利用日・店舗から実施中のキャンペーンを入れる（店舗の子キャンペーン優先、無ければ全店キャンペーン）</t>
+  </si>
+  <si>
+    <t>RepeatWithin30Days__c</t>
+  </si>
+  <si>
+    <t>30日以内にリピート</t>
+  </si>
+  <si>
+    <t>キャンペーンでの購入のあと、30日以内に同じカードで購入があると自動でオン</t>
+  </si>
+  <si>
+    <t>RepeatCount__c</t>
+  </si>
+  <si>
+    <t>リピート件数</t>
+  </si>
+  <si>
+    <t>数式（数値）</t>
+  </si>
+  <si>
+    <t>リピートなら1。レポートのリピート率の計算に使う</t>
+  </si>
+  <si>
+    <t>項目定義書　－ キャンペーンオブジェクト（Campaign）</t>
+  </si>
+  <si>
+    <t>キャンペーン名</t>
+  </si>
+  <si>
+    <t>例：秋のブレンドフェア_渋谷店</t>
+  </si>
+  <si>
+    <t>ParentId</t>
+  </si>
+  <si>
+    <t>親キャンペーン</t>
+  </si>
+  <si>
+    <t>複数店舗で行うときは、親（集計用・無効）の下に店舗ごとの子キャンペーンを作る</t>
+  </si>
+  <si>
+    <t>対象店舗</t>
+  </si>
+  <si>
+    <t>対象店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。グローバル選択リスト「店舗」。空欄の有効なキャンペーンは全店キャンペーンとして扱う</t>
+  </si>
+  <si>
+    <t>IsActive</t>
+  </si>
+  <si>
+    <t>有効</t>
+  </si>
+  <si>
+    <t>有効なキャンペーンだけ、ポイント履歴に自動で紐づく</t>
+  </si>
+  <si>
+    <t>StartDate</t>
+  </si>
+  <si>
+    <t>開始日</t>
+  </si>
+  <si>
+    <t>この期間の購入を自動で紐づける</t>
+  </si>
+  <si>
+    <t>EndDate</t>
+  </si>
+  <si>
+    <t>終了日</t>
+  </si>
+  <si>
+    <t>キャンペーン種別</t>
+  </si>
+  <si>
+    <t>BudgetedCost</t>
+  </si>
+  <si>
+    <t>予算</t>
+  </si>
+  <si>
+    <t>ActualCost</t>
+  </si>
+  <si>
+    <t>実際の費用</t>
+  </si>
+  <si>
+    <t>法人商談の受注額と比べて費用対効果を見る</t>
+  </si>
+  <si>
+    <t>NumberOfResponses</t>
+  </si>
+  <si>
+    <t>レスポンス数</t>
+  </si>
+  <si>
+    <t>反応した会員数</t>
+  </si>
+  <si>
+    <t>Salesforce標準。フロー「ポイント履歴：リピートと反応の記録」で、案内した会員が購入するとレスポンスありになる</t>
   </si>
 </sst>
 </file>
@@ -3496,7 +3605,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3758,11 +3867,388 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="7">
+        <v>9</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -3778,7 +4264,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>283</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3834,115 +4320,111 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>245</v>
+        <v>284</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>245</v>
+        <v>284</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8"/>
+        <v>20</v>
+      </c>
+      <c r="E4" s="7">
+        <v>80</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>246</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>247</v>
+        <v>286</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>248</v>
+        <v>287</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>249</v>
+        <v>161</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="F5" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="F5" s="8"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>250</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>252</v>
+        <v>290</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="7"/>
-      <c r="F6" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="7" t="s">
-        <v>253</v>
+        <v>108</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>254</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>255</v>
+        <v>292</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="7">
-        <v>9</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>21</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>258</v>
+        <v>295</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
@@ -3951,114 +4433,118 @@
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>105</v>
+        <v>298</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>147</v>
+        <v>299</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>147</v>
+        <v>299</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
-      <c r="G9" s="7" t="s">
-        <v>108</v>
-      </c>
+      <c r="G9" s="7"/>
       <c r="H9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>261</v>
-      </c>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>262</v>
+        <v>27</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>263</v>
+        <v>199</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="E10" s="7"/>
-      <c r="F10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7" t="s">
+        <v>209</v>
+      </c>
       <c r="H10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>239</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>264</v>
+        <v>301</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="D11" s="7"/>
+        <v>302</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="E11" s="7"/>
       <c r="F11" s="8"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="9" t="s">
-        <v>267</v>
-      </c>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9"/>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="D12" s="7"/>
+        <v>304</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="E12" s="7"/>
       <c r="F12" s="8"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="I12" s="9" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>272</v>
+        <v>307</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="D13" s="7"/>
+        <v>308</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="E13" s="7"/>
       <c r="F13" s="8"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>130</v>
+      </c>
       <c r="I13" s="9" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>

--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="469">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -303,6 +303,21 @@
     <t>オフィス/飲食店・カフェ</t>
   </si>
   <si>
+    <t>NameKey__c</t>
+  </si>
+  <si>
+    <t>会社名（照合用）</t>
+  </si>
+  <si>
+    <t>会社名（照合用）（カスタム）</t>
+  </si>
+  <si>
+    <t>自動</t>
+  </si>
+  <si>
+    <t>カスタム項目。フロー「取引先：照合用の会社名」で設定。重複ルール「会社名が同じ取引先」で使う（例：（株）ＡＢＣオフィスサービス と ABCオフィスサービス株式会社 を同じ会社と判定）</t>
+  </si>
+  <si>
     <t>項目定義書　－ 取引先責任者オブジェクト（Contact）</t>
   </si>
   <si>
@@ -525,9 +540,6 @@
     <t>パーセント</t>
   </si>
   <si>
-    <t>自動</t>
-  </si>
-  <si>
     <t>フェーズに連動して自動設定</t>
   </si>
   <si>
@@ -600,178 +612,220 @@
     <t>商談 種別</t>
   </si>
   <si>
-    <t>商談種別</t>
+    <t>営業区分</t>
+  </si>
+  <si>
+    <t>新規開拓/アップセル（既存のお客様）</t>
+  </si>
+  <si>
+    <t>標準選択リスト（表示ラベルを変更）。空欄ならフロー「商談：営業区分と担当店舗」が、取引先に受注済みの商談があればアップセル、無ければ新規開拓にする。旧値 オフィス定期便／業務用卸 は無効</t>
+  </si>
+  <si>
+    <t>CampaignId</t>
+  </si>
+  <si>
+    <t>主キャンペーン</t>
+  </si>
+  <si>
+    <t>キャンペーン</t>
+  </si>
+  <si>
+    <t>参照（Campaign）</t>
+  </si>
+  <si>
+    <t>キャンペーン効果（法人の受注額）の集計に使う</t>
+  </si>
+  <si>
+    <t>LastContactDate__c</t>
+  </si>
+  <si>
+    <t>最終連絡日</t>
+  </si>
+  <si>
+    <t>最終連絡日（カスタム）</t>
+  </si>
+  <si>
+    <t>NextStep</t>
+  </si>
+  <si>
+    <t>次のステップ</t>
+  </si>
+  <si>
+    <t>次にやること</t>
+  </si>
+  <si>
+    <t>Salesforce標準</t>
+  </si>
+  <si>
+    <t>OpportunityLineItem</t>
+  </si>
+  <si>
+    <t>商談商品</t>
+  </si>
+  <si>
+    <t>見積の明細</t>
+  </si>
+  <si>
+    <t>関連リスト</t>
+  </si>
+  <si>
+    <t>Salesforce標準。見積書の品名・数量・単価を商談商品として登録</t>
+  </si>
+  <si>
+    <t>ProductCategory__c</t>
+  </si>
+  <si>
+    <t>商材</t>
+  </si>
+  <si>
+    <t>商材（カスタム）</t>
   </si>
   <si>
     <t>オフィス定期便/業務用卸</t>
   </si>
   <si>
+    <t>カスタム項目。#5 で種別に入れていた値をここに移した</t>
+  </si>
+  <si>
+    <t>項目定義書　－ リードオブジェクト（Lead）</t>
+  </si>
+  <si>
+    <t>LeadId</t>
+  </si>
+  <si>
+    <t>リードID</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>会社名</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>ステータス</t>
+  </si>
+  <si>
+    <t>リードステータス</t>
+  </si>
+  <si>
+    <t>新規/対応中/商談化/失注/対象外</t>
+  </si>
+  <si>
+    <t>リード発生源</t>
+  </si>
+  <si>
+    <t>飛び込み/展示会/Web/紹介/広告/その他</t>
+  </si>
+  <si>
+    <t>標準選択リストに「飛び込み」を追加</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>評価</t>
+  </si>
+  <si>
+    <t>リード評価</t>
+  </si>
+  <si>
+    <t>Hot/Warm/Cold</t>
+  </si>
+  <si>
+    <t>メモ</t>
+  </si>
+  <si>
+    <t>リードオーナー</t>
+  </si>
+  <si>
+    <t>IsConverted</t>
+  </si>
+  <si>
+    <t>商談化済み</t>
+  </si>
+  <si>
+    <t>商談化フラグ</t>
+  </si>
+  <si>
+    <t>チェックボックス</t>
+  </si>
+  <si>
+    <t>商談化時に自動でTrue</t>
+  </si>
+  <si>
+    <t>カスタム項目。取引の開始で取引先の担当店舗に引き継ぐ</t>
+  </si>
+  <si>
+    <t>カスタム項目。取引の開始で取引先の担当スタッフに引き継ぐ</t>
+  </si>
+  <si>
+    <t>最終訪問日</t>
+  </si>
+  <si>
+    <t>最終訪問日（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。取引の開始で商談の最終連絡日に引き継ぐ</t>
+  </si>
+  <si>
+    <t>CompanyKey__c</t>
+  </si>
+  <si>
+    <t>カスタム項目。フロー「リード：照合用の会社名」で、株式会社・（株）・空白などを除き全角英数字を半角にした値。重複ルール「リードと既存の取引先」で使う</t>
+  </si>
+  <si>
+    <t>項目定義書　－ ユーザーオブジェクト（User）</t>
+  </si>
+  <si>
+    <t>所属店舗</t>
+  </si>
+  <si>
+    <t>所属店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。グローバル選択リスト「店舗」(Store)を使用。ケース・商談の店舗の初期値になる</t>
+  </si>
+  <si>
+    <t>項目定義書　－ ケースオブジェクト（Case）</t>
+  </si>
+  <si>
+    <t>CaseNumber</t>
+  </si>
+  <si>
+    <t>ケース番号</t>
+  </si>
+  <si>
+    <t>取引先責任者</t>
+  </si>
+  <si>
+    <t>お客様（会員）</t>
+  </si>
+  <si>
+    <t>参照（Contact）</t>
+  </si>
+  <si>
+    <t>問い合わせたお客様</t>
+  </si>
+  <si>
+    <t>お客様の取引先から自動設定</t>
+  </si>
+  <si>
+    <t>カスタム項目。グローバル選択リスト「店舗」。空欄なら作成者の所属店舗をフロー「ケース：店舗の初期値」で設定</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>問い合わせ種別</t>
+  </si>
+  <si>
+    <t>商品について/ギフト/定期便/法人のお取引/クレーム/その他</t>
+  </si>
+  <si>
     <t>標準選択リストに値を追加（既存の値は残している）</t>
-  </si>
-  <si>
-    <t>CampaignId</t>
-  </si>
-  <si>
-    <t>主キャンペーン</t>
-  </si>
-  <si>
-    <t>キャンペーン</t>
-  </si>
-  <si>
-    <t>参照（Campaign）</t>
-  </si>
-  <si>
-    <t>キャンペーン効果（法人の受注額）の集計に使う</t>
-  </si>
-  <si>
-    <t>LastContactDate__c</t>
-  </si>
-  <si>
-    <t>最終連絡日</t>
-  </si>
-  <si>
-    <t>最終連絡日（カスタム）</t>
-  </si>
-  <si>
-    <t>NextStep</t>
-  </si>
-  <si>
-    <t>次のステップ</t>
-  </si>
-  <si>
-    <t>次にやること</t>
-  </si>
-  <si>
-    <t>Salesforce標準</t>
-  </si>
-  <si>
-    <t>OpportunityLineItem</t>
-  </si>
-  <si>
-    <t>商談商品</t>
-  </si>
-  <si>
-    <t>見積の明細</t>
-  </si>
-  <si>
-    <t>関連リスト</t>
-  </si>
-  <si>
-    <t>Salesforce標準。見積書の品名・数量・単価を商談商品として登録</t>
-  </si>
-  <si>
-    <t>項目定義書　－ リードオブジェクト（Lead）</t>
-  </si>
-  <si>
-    <t>LeadId</t>
-  </si>
-  <si>
-    <t>リードID</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>会社名</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>ステータス</t>
-  </si>
-  <si>
-    <t>リードステータス</t>
-  </si>
-  <si>
-    <t>新規/対応中/商談化/失注/対象外</t>
-  </si>
-  <si>
-    <t>リード発生源</t>
-  </si>
-  <si>
-    <t>展示会/Web/紹介/広告/その他</t>
-  </si>
-  <si>
-    <t>Rating</t>
-  </si>
-  <si>
-    <t>評価</t>
-  </si>
-  <si>
-    <t>リード評価</t>
-  </si>
-  <si>
-    <t>Hot/Warm/Cold</t>
-  </si>
-  <si>
-    <t>メモ</t>
-  </si>
-  <si>
-    <t>リードオーナー</t>
-  </si>
-  <si>
-    <t>IsConverted</t>
-  </si>
-  <si>
-    <t>商談化済み</t>
-  </si>
-  <si>
-    <t>商談化フラグ</t>
-  </si>
-  <si>
-    <t>チェックボックス</t>
-  </si>
-  <si>
-    <t>商談化時に自動でTrue</t>
-  </si>
-  <si>
-    <t>項目定義書　－ ユーザーオブジェクト（User）</t>
-  </si>
-  <si>
-    <t>所属店舗</t>
-  </si>
-  <si>
-    <t>所属店舗（カスタム）</t>
-  </si>
-  <si>
-    <t>カスタム項目。グローバル選択リスト「店舗」(Store)を使用。ケース・商談の店舗の初期値になる</t>
-  </si>
-  <si>
-    <t>項目定義書　－ ケースオブジェクト（Case）</t>
-  </si>
-  <si>
-    <t>CaseNumber</t>
-  </si>
-  <si>
-    <t>ケース番号</t>
-  </si>
-  <si>
-    <t>取引先責任者</t>
-  </si>
-  <si>
-    <t>お客様（会員）</t>
-  </si>
-  <si>
-    <t>参照（Contact）</t>
-  </si>
-  <si>
-    <t>問い合わせたお客様</t>
-  </si>
-  <si>
-    <t>お客様の取引先から自動設定</t>
-  </si>
-  <si>
-    <t>カスタム項目。グローバル選択リスト「店舗」。空欄なら作成者の所属店舗をフロー「ケース：店舗の初期値」で設定</t>
-  </si>
-  <si>
-    <t>種別</t>
-  </si>
-  <si>
-    <t>問い合わせ種別</t>
-  </si>
-  <si>
-    <t>商品について/ギフト/定期便/法人のお取引/クレーム/その他</t>
   </si>
   <si>
     <t>Origin</t>
@@ -1957,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -1982,7 +2036,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2454,6 +2508,31 @@
       </c>
       <c r="I21" s="9" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7">
+        <v>255</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2480,7 +2559,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2491,7 +2570,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2536,10 +2615,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>20</v>
@@ -2555,18 +2634,18 @@
         <v>9</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2580,18 +2659,18 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>20</v>
@@ -2605,18 +2684,18 @@
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2624,24 +2703,24 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -2649,24 +2728,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>20</v>
@@ -2685,13 +2764,13 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -2699,7 +2778,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>25</v>
@@ -2710,16 +2789,16 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="8"/>
@@ -2728,7 +2807,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2736,10 +2815,10 @@
         <v>61</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>64</v>
@@ -2753,18 +2832,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>38</v>
@@ -2776,7 +2855,7 @@
         <v>25</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -2784,7 +2863,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2804,7 +2883,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2815,7 +2894,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2860,13 +2939,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -2875,18 +2954,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2900,21 +2979,21 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
@@ -2929,10 +3008,10 @@
         <v>79</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2946,18 +3025,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>20</v>
@@ -2974,16 +3053,16 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
@@ -2992,18 +3071,18 @@
         <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>20</v>
@@ -3017,18 +3096,18 @@
         <v>25</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
@@ -3042,18 +3121,18 @@
         <v>25</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>20</v>
@@ -3067,18 +3146,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>42</v>
@@ -3095,13 +3174,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>38</v>
@@ -3116,13 +3195,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>38</v>
@@ -3137,13 +3216,13 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>29</v>
@@ -3151,7 +3230,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="7" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>25</v>
@@ -3160,16 +3239,16 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="8"/>
@@ -3178,21 +3257,21 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="8"/>
@@ -3201,7 +3280,7 @@
         <v>25</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -3209,7 +3288,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3229,7 +3308,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3240,7 +3319,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3282,16 +3361,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8" t="s">
@@ -3305,16 +3384,16 @@
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -3323,18 +3402,18 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
@@ -3342,24 +3421,24 @@
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="7" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -3373,26 +3452,26 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
@@ -3403,13 +3482,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>73</v>
@@ -3429,7 +3508,7 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -3449,7 +3528,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3502,10 +3581,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3522,7 +3601,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3530,13 +3609,13 @@
         <v>13</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8" t="s">
@@ -3547,18 +3626,18 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
@@ -3577,13 +3656,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -3600,13 +3679,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>20</v>
@@ -3623,13 +3702,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>20</v>
@@ -3646,16 +3725,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E10" s="10">
         <v>80</v>
@@ -3675,7 +3754,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>50</v>
@@ -3692,13 +3771,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>50</v>
@@ -3715,13 +3794,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>45</v>
@@ -3739,7 +3818,7 @@
         <v>56</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>58</v>
@@ -3760,10 +3839,10 @@
         <v>79</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>29</v>
@@ -3777,18 +3856,18 @@
         <v>25</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>73</v>
@@ -3805,13 +3884,13 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>29</v>
@@ -3819,7 +3898,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="8"/>
       <c r="G17" s="7" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>25</v>
@@ -3830,13 +3909,13 @@
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>20</v>
@@ -3850,18 +3929,18 @@
         <v>25</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>20</v>
@@ -3880,13 +3959,13 @@
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>20</v>
@@ -3900,18 +3979,18 @@
         <v>25</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>42</v>
@@ -3925,18 +4004,18 @@
         <v>25</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>73</v>
@@ -3986,7 +4065,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -4000,7 +4079,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4053,10 +4132,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4073,7 +4152,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4081,10 +4160,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -4100,7 +4179,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4111,10 +4190,10 @@
         <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="20" t="s">
@@ -4128,13 +4207,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -4144,24 +4223,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -4178,13 +4257,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -4199,36 +4278,36 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -4236,7 +4315,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -4251,7 +4330,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -4271,7 +4350,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -4289,13 +4368,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -4314,13 +4393,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -4328,13 +4407,13 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4342,10 +4421,10 @@
         <v>79</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>29</v>
@@ -4359,18 +4438,18 @@
         <v>25</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>38</v>
@@ -4382,7 +4461,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4390,10 +4469,10 @@
         <v>27</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>29</v>
@@ -4401,27 +4480,27 @@
       <c r="E18" s="7"/>
       <c r="F18" s="8"/>
       <c r="G18" s="7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
@@ -4430,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4460,13 +4539,13 @@
     </row>
     <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>73</v>
@@ -4483,13 +4562,13 @@
     </row>
     <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>20</v>
@@ -4503,21 +4582,21 @@
         <v>25</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="8"/>
@@ -4526,7 +4605,32 @@
         <v>25</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
+      </c>
+    </row>
+    <row r="24" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -4539,7 +4643,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -4553,7 +4657,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4606,10 +4710,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4626,18 +4730,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -4656,13 +4760,13 @@
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
@@ -4679,13 +4783,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -4704,13 +4808,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>20</v>
@@ -4727,16 +4831,16 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E9" s="7">
         <v>80</v>
@@ -4773,13 +4877,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -4789,7 +4893,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -4798,13 +4902,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -4812,22 +4916,24 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="12"/>
+      <c r="I12" s="12" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -4835,7 +4941,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -4850,7 +4956,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -4870,7 +4976,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -4888,16 +4994,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -4906,7 +5012,105 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>232</v>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7">
+        <v>40</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7">
+        <v>255</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4933,7 +5137,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4989,10 +5193,10 @@
         <v>79</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>29</v>
@@ -5006,7 +5210,7 @@
         <v>25</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -5034,7 +5238,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5087,16 +5291,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E4" s="7">
         <v>30</v>
@@ -5107,21 +5311,21 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -5130,7 +5334,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5138,22 +5342,22 @@
         <v>13</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5161,10 +5365,10 @@
         <v>79</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -5178,7 +5382,7 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5186,10 +5390,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -5197,24 +5401,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>193</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -5224,24 +5428,24 @@
         <v>21</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -5251,24 +5455,24 @@
         <v>21</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
@@ -5291,7 +5495,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>64</v>
@@ -5311,13 +5515,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="8" t="s">
@@ -5328,18 +5532,18 @@
         <v>9</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>73</v>
@@ -5351,7 +5555,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5359,10 +5563,10 @@
         <v>84</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>20</v>
@@ -5381,13 +5585,13 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>64</v>
@@ -5406,13 +5610,13 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>20</v>
@@ -5426,7 +5630,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -5454,7 +5658,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5510,13 +5714,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -5525,18 +5729,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -5552,21 +5756,21 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
@@ -5575,41 +5779,41 @@
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -5617,24 +5821,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -5648,18 +5852,18 @@
         <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>73</v>
@@ -5671,30 +5875,30 @@
         <v>25</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="8"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5702,10 +5906,10 @@
         <v>56</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>59</v>
@@ -5747,7 +5951,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5803,13 +6007,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -5818,21 +6022,21 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8" t="s">
@@ -5843,18 +6047,18 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
@@ -5864,24 +6068,24 @@
         <v>21</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>42</v>
@@ -5897,18 +6101,18 @@
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>38</v>
@@ -5920,7 +6124,7 @@
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5928,10 +6132,10 @@
         <v>79</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -5945,18 +6149,18 @@
         <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>73</v>
@@ -5970,18 +6174,18 @@
         <v>9</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -5989,18 +6193,18 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="9" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -6008,18 +6212,18 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="9" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -6027,76 +6231,76 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="8"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="8"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -6124,7 +6328,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6180,10 +6384,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>20</v>
@@ -6199,21 +6403,21 @@
         <v>9</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -6222,7 +6426,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6230,10 +6434,10 @@
         <v>79</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
@@ -6247,21 +6451,21 @@
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
@@ -6270,18 +6474,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>73</v>
@@ -6293,18 +6497,18 @@
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>73</v>
@@ -6322,10 +6526,10 @@
         <v>27</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -6333,7 +6537,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>25</v>
@@ -6342,13 +6546,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>38</v>
@@ -6363,13 +6567,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>38</v>
@@ -6381,18 +6585,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>42</v>
@@ -6401,10 +6605,10 @@
       <c r="F13" s="8"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -16,13 +16,16 @@
     <sheet sheetId="7" name="ポイントカード" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="ポイント履歴" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="キャンペーン" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="商品" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="POS売上明細" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="キャンペーンメンバー" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="451">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -261,6 +264,45 @@
     <t>カスタム項目、Issue #1</t>
   </si>
   <si>
+    <t>Store__c</t>
+  </si>
+  <si>
+    <t>担当店舗</t>
+  </si>
+  <si>
+    <t>担当店舗（カスタム）</t>
+  </si>
+  <si>
+    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ/本社</t>
+  </si>
+  <si>
+    <t>カスタム項目。法人の窓口になる店舗（1社1店舗）。同じ会社への二重営業を防ぐ</t>
+  </si>
+  <si>
+    <t>StaffName__c</t>
+  </si>
+  <si>
+    <t>担当スタッフ</t>
+  </si>
+  <si>
+    <t>担当スタッフ（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。店舗スタッフはSalesforceのユーザーでない場合があるためテキスト</t>
+  </si>
+  <si>
+    <t>CustomerCategory__c</t>
+  </si>
+  <si>
+    <t>法人区分</t>
+  </si>
+  <si>
+    <t>法人区分（カスタム）</t>
+  </si>
+  <si>
+    <t>オフィス/飲食店・カフェ</t>
+  </si>
+  <si>
     <t>項目定義書　－ 取引先責任者オブジェクト（Contact）</t>
   </si>
   <si>
@@ -339,21 +381,90 @@
     <t>取引先責任者オーナー</t>
   </si>
   <si>
-    <t>Store__c</t>
-  </si>
-  <si>
     <t>よく行く店舗</t>
   </si>
   <si>
     <t>よく行く店舗（カスタム）</t>
   </si>
   <si>
-    <t>吉祥寺本店/自由が丘店/二子玉川店/渋谷店/新宿店/池袋店/オンラインショップ/本社</t>
-  </si>
-  <si>
     <t>カスタム項目。グローバル選択リスト「店舗」。個人のお客様（会員）が主に利用する店舗</t>
   </si>
   <si>
+    <t>RegisteredDate__c</t>
+  </si>
+  <si>
+    <t>登録日</t>
+  </si>
+  <si>
+    <t>登録日（カスタム）</t>
+  </si>
+  <si>
+    <t>RegistrationChannel__c</t>
+  </si>
+  <si>
+    <t>登録経路</t>
+  </si>
+  <si>
+    <t>登録経路（カスタム）</t>
+  </si>
+  <si>
+    <t>店舗の顧客台帳/常連さんメモ/オンライン会員/ポイントカード申込</t>
+  </si>
+  <si>
+    <t>Nickname__c</t>
+  </si>
+  <si>
+    <t>呼び名</t>
+  </si>
+  <si>
+    <t>呼び名（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。例：鈴木さん、先生</t>
+  </si>
+  <si>
+    <t>Features__c</t>
+  </si>
+  <si>
+    <t>見た目・特徴</t>
+  </si>
+  <si>
+    <t>見た目・特徴（カスタム）</t>
+  </si>
+  <si>
+    <t>UsualOrder__c</t>
+  </si>
+  <si>
+    <t>いつもの</t>
+  </si>
+  <si>
+    <t>いつもの（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。いつも買う商品・好み</t>
+  </si>
+  <si>
+    <t>PaperStampCount__c</t>
+  </si>
+  <si>
+    <t>紙スタンプ数</t>
+  </si>
+  <si>
+    <t>紙スタンプ数（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。紙のスタンプカードからポイントカードへの移行に使う</t>
+  </si>
+  <si>
+    <t>LastVisitDate__c</t>
+  </si>
+  <si>
+    <t>最終来店日</t>
+  </si>
+  <si>
+    <t>最終来店日（カスタム）</t>
+  </si>
+  <si>
     <t>項目定義書　－ 商談オブジェクト（Opportunity）</t>
   </si>
   <si>
@@ -513,6 +624,42 @@
     <t>キャンペーン効果（法人の受注額）の集計に使う</t>
   </si>
   <si>
+    <t>LastContactDate__c</t>
+  </si>
+  <si>
+    <t>最終連絡日</t>
+  </si>
+  <si>
+    <t>最終連絡日（カスタム）</t>
+  </si>
+  <si>
+    <t>NextStep</t>
+  </si>
+  <si>
+    <t>次のステップ</t>
+  </si>
+  <si>
+    <t>次にやること</t>
+  </si>
+  <si>
+    <t>Salesforce標準</t>
+  </si>
+  <si>
+    <t>OpportunityLineItem</t>
+  </si>
+  <si>
+    <t>商談商品</t>
+  </si>
+  <si>
+    <t>見積の明細</t>
+  </si>
+  <si>
+    <t>関連リスト</t>
+  </si>
+  <si>
+    <t>Salesforce標準。見積書の品名・数量・単価を商談商品として登録</t>
+  </si>
+  <si>
     <t>項目定義書　－ リードオブジェクト（Lead）</t>
   </si>
   <si>
@@ -600,9 +747,6 @@
     <t>ケース番号</t>
   </si>
   <si>
-    <t>Salesforce標準</t>
-  </si>
-  <si>
     <t>取引先責任者</t>
   </si>
   <si>
@@ -675,6 +819,45 @@
     <t>未割り当ては「本社カスタマーサクセス」キュー</t>
   </si>
   <si>
+    <t>ReceivedDate__c</t>
+  </si>
+  <si>
+    <t>受付日</t>
+  </si>
+  <si>
+    <t>受付日（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。過去の問い合わせ記録の取り込み用</t>
+  </si>
+  <si>
+    <t>受けたスタッフ</t>
+  </si>
+  <si>
+    <t>受けたスタッフ（カスタム）</t>
+  </si>
+  <si>
+    <t>Resolution__c</t>
+  </si>
+  <si>
+    <t>対応内容</t>
+  </si>
+  <si>
+    <t>対応内容（カスタム）</t>
+  </si>
+  <si>
+    <t>SuppliedName</t>
+  </si>
+  <si>
+    <t>Web 名</t>
+  </si>
+  <si>
+    <t>お客様名（未登録）</t>
+  </si>
+  <si>
+    <t>Salesforce標準。会員でないお客様の名前</t>
+  </si>
+  <si>
     <t>項目定義書　－ ポイントカードオブジェクト（PointCard__c）</t>
   </si>
   <si>
@@ -952,6 +1135,249 @@
   </si>
   <si>
     <t>Salesforce標準。フロー「ポイント履歴：リピートと反応の記録」で、案内した会員が購入するとレスポンスありになる</t>
+  </si>
+  <si>
+    <t>項目定義書　－ 商品オブジェクト（Product2）</t>
+  </si>
+  <si>
+    <t>商品名</t>
+  </si>
+  <si>
+    <t>商品マスタの商品名</t>
+  </si>
+  <si>
+    <t>ProductCode</t>
+  </si>
+  <si>
+    <t>商品コード</t>
+  </si>
+  <si>
+    <t>容量ごとのコード（例：B001-200）。元の商品マスタは商品コード×容量の価格表</t>
+  </si>
+  <si>
+    <t>BaseCode__c</t>
+  </si>
+  <si>
+    <t>商品コード（容量共通）</t>
+  </si>
+  <si>
+    <t>商品コード（容量共通）（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。商品マスタの商品コード（例：B001）</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>商品ファミリ</t>
+  </si>
+  <si>
+    <t>ブレンド/シングルオリジン/季節限定/ギフト</t>
+  </si>
+  <si>
+    <t>標準選択リストに値を追加</t>
+  </si>
+  <si>
+    <t>Size__c</t>
+  </si>
+  <si>
+    <t>内容量</t>
+  </si>
+  <si>
+    <t>内容量（カスタム）</t>
+  </si>
+  <si>
+    <t>100g/200g/500g/セット</t>
+  </si>
+  <si>
+    <t>カスタム項目。容量ごとに1商品</t>
+  </si>
+  <si>
+    <t>Origin__c</t>
+  </si>
+  <si>
+    <t>産地</t>
+  </si>
+  <si>
+    <t>産地（カスタム）</t>
+  </si>
+  <si>
+    <t>RoastLevel__c</t>
+  </si>
+  <si>
+    <t>焙煎度</t>
+  </si>
+  <si>
+    <t>焙煎度（カスタム）</t>
+  </si>
+  <si>
+    <t>浅煎り/中煎り/中深煎り/深煎り</t>
+  </si>
+  <si>
+    <t>季節限定の販売期間外は無効にする</t>
+  </si>
+  <si>
+    <t>商品説明</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>例：10月〜11月限定</t>
+  </si>
+  <si>
+    <t>（価格）</t>
+  </si>
+  <si>
+    <t>標準価格表</t>
+  </si>
+  <si>
+    <t>税込価格</t>
+  </si>
+  <si>
+    <t>標準価格表に容量ごとの税込価格を登録。商談商品（見積の明細）で使う</t>
+  </si>
+  <si>
+    <t>項目定義書　－ POS売上明細オブジェクト（POSSale__c）</t>
+  </si>
+  <si>
+    <t>明細番号</t>
+  </si>
+  <si>
+    <t>POS-000000 の形式</t>
+  </si>
+  <si>
+    <t>TransactionNo__c</t>
+  </si>
+  <si>
+    <t>取引番号</t>
+  </si>
+  <si>
+    <t>外部ID。POSの取引番号（例：T20261001-S02-0001）</t>
+  </si>
+  <si>
+    <t>SoldAt__c</t>
+  </si>
+  <si>
+    <t>日時</t>
+  </si>
+  <si>
+    <t>日付/時間</t>
+  </si>
+  <si>
+    <t>グローバル選択リスト「店舗」。POSの店舗コード S01=吉祥寺本店 S02=自由が丘店 S03=二子玉川店 S04=渋谷店 S05=新宿店 S06=池袋店</t>
+  </si>
+  <si>
+    <t>RegisterNo__c</t>
+  </si>
+  <si>
+    <t>レジ番号</t>
+  </si>
+  <si>
+    <t>Product__c</t>
+  </si>
+  <si>
+    <t>商品</t>
+  </si>
+  <si>
+    <t>参照（Product2）</t>
+  </si>
+  <si>
+    <t>取り込み時に 商品コード＋内容量 で商品を探して設定</t>
+  </si>
+  <si>
+    <t>ProductCode__c</t>
+  </si>
+  <si>
+    <t>POSの値をそのまま保存</t>
+  </si>
+  <si>
+    <t>ProductName__c</t>
+  </si>
+  <si>
+    <t>Quantity__c</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>UnitPrice__c</t>
+  </si>
+  <si>
+    <t>単価（税込）</t>
+  </si>
+  <si>
+    <t>Amount__c</t>
+  </si>
+  <si>
+    <t>金額（税込）</t>
+  </si>
+  <si>
+    <t>PaymentMethod__c</t>
+  </si>
+  <si>
+    <t>支払方法</t>
+  </si>
+  <si>
+    <t>現金/クレジット/電子マネー/QRコード決済</t>
+  </si>
+  <si>
+    <t>参照（PointCard__c）</t>
+  </si>
+  <si>
+    <t>会員の購入なら紐づける（レジでカードを読み取ったとき）</t>
+  </si>
+  <si>
+    <t>会員以外も含めたキャンペーン効果の集計に使う</t>
+  </si>
+  <si>
+    <t>項目定義書　－ キャンペーンメンバーオブジェクト（CampaignMember）</t>
+  </si>
+  <si>
+    <t>同じ会員を同じキャンペーンに二重登録できない（二重送付の防止）</t>
+  </si>
+  <si>
+    <t>送信/レスポンスあり</t>
+  </si>
+  <si>
+    <t>購入するとフローで自動的にレスポンスあり</t>
+  </si>
+  <si>
+    <t>SourceList__c</t>
+  </si>
+  <si>
+    <t>元のリスト</t>
+  </si>
+  <si>
+    <t>元のリスト（カスタム）</t>
+  </si>
+  <si>
+    <t>カスタム項目。どの店舗の送付リストから来たか</t>
+  </si>
+  <si>
+    <t>SendChannel__c</t>
+  </si>
+  <si>
+    <t>送り方</t>
+  </si>
+  <si>
+    <t>送り方（カスタム）</t>
+  </si>
+  <si>
+    <t>複数選択リスト</t>
+  </si>
+  <si>
+    <t>メール/DM/LINE</t>
+  </si>
+  <si>
+    <t>SentDate__c</t>
+  </si>
+  <si>
+    <t>送付日</t>
+  </si>
+  <si>
+    <t>送付日（カスタム）</t>
   </si>
 </sst>
 </file>
@@ -1531,7 +1957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -1955,6 +2381,81 @@
         <v>78</v>
       </c>
     </row>
+    <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7">
+        <v>40</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
@@ -1963,9 +2464,978 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7">
+        <v>255</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7">
+        <v>255</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="7">
+        <v>10</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7">
+        <v>100</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4000</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>403</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7">
+        <v>30</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="7">
+        <v>20</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="7">
+        <v>100</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="7">
+        <v>20</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="7">
+        <v>5</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="9"/>
+    </row>
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="22.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="6" max="6" width="8.69921875" customWidth="1"/>
+    <col min="7" max="7" width="40.69921875" customWidth="1"/>
+    <col min="8" max="8" width="12.69921875" customWidth="1"/>
+    <col min="9" max="9" width="35.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -1979,7 +3449,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2032,10 +3502,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2052,7 +3522,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2060,13 +3530,13 @@
         <v>13</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8" t="s">
@@ -2077,18 +3547,18 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
@@ -2107,13 +3577,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2130,13 +3600,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>20</v>
@@ -2153,13 +3623,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>20</v>
@@ -2176,16 +3646,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E10" s="10">
         <v>80</v>
@@ -2205,7 +3675,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>50</v>
@@ -2222,13 +3692,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>50</v>
@@ -2245,13 +3715,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>45</v>
@@ -2269,7 +3739,7 @@
         <v>56</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>58</v>
@@ -2287,13 +3757,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>29</v>
@@ -2301,13 +3771,209 @@
       <c r="E15" s="7"/>
       <c r="F15" s="8"/>
       <c r="G15" s="7" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>109</v>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="7">
+        <v>40</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="7">
+        <v>255</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7">
+        <v>255</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="7">
+        <v>40</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2320,7 +3986,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.45" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2334,7 +4000,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2387,10 +4053,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2407,7 +4073,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2415,10 +4081,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2434,7 +4100,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2445,10 +4111,10 @@
         <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="20" t="s">
@@ -2462,13 +4128,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2478,24 +4144,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -2512,13 +4178,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -2533,36 +4199,36 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -2570,7 +4236,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -2585,7 +4251,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -2605,7 +4271,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -2623,13 +4289,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -2648,13 +4314,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -2662,24 +4328,24 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>29</v>
@@ -2687,24 +4353,24 @@
       <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="7" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>38</v>
@@ -2716,7 +4382,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2724,10 +4390,10 @@
         <v>27</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>29</v>
@@ -2735,27 +4401,27 @@
       <c r="E18" s="7"/>
       <c r="F18" s="8"/>
       <c r="G18" s="7" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
@@ -2764,7 +4430,103 @@
         <v>25</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>162</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="7">
+        <v>40</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="7">
+        <v>255</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -2791,7 +4553,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2844,10 +4606,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -2864,18 +4626,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2894,13 +4656,13 @@
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
@@ -2917,13 +4679,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -2942,13 +4704,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>20</v>
@@ -2965,16 +4727,16 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E9" s="7">
         <v>80</v>
@@ -3011,13 +4773,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>169</v>
+        <v>217</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>170</v>
+        <v>218</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -3027,7 +4789,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>171</v>
+        <v>219</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -3036,13 +4798,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>172</v>
+        <v>220</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -3050,7 +4812,7 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
@@ -3059,13 +4821,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>174</v>
+        <v>222</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>175</v>
+        <v>223</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -3073,7 +4835,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -3088,7 +4850,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -3108,7 +4870,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>179</v>
+        <v>227</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -3126,16 +4888,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>180</v>
+        <v>228</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>181</v>
+        <v>229</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>182</v>
+        <v>230</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -3144,7 +4906,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>184</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3171,7 +4933,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>233</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3224,13 +4986,13 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>187</v>
+        <v>235</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>29</v>
@@ -3238,13 +5000,13 @@
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
       <c r="G4" s="7" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3258,7 +5020,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -3272,7 +5034,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3325,16 +5087,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>191</v>
+        <v>239</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E4" s="7">
         <v>30</v>
@@ -3345,21 +5107,21 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>193</v>
+        <v>240</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -3368,7 +5130,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>196</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3376,33 +5138,33 @@
         <v>13</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>197</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -3410,13 +5172,13 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>198</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3424,10 +5186,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -3435,24 +5197,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -3462,24 +5224,24 @@
         <v>21</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>168</v>
+        <v>216</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -3489,24 +5251,24 @@
         <v>21</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>210</v>
+        <v>257</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
@@ -3529,7 +5291,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>64</v>
@@ -3549,13 +5311,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>214</v>
+        <v>261</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>215</v>
+        <v>262</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="8" t="s">
@@ -3566,7 +5328,105 @@
         <v>9</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>216</v>
+        <v>263</v>
+      </c>
+    </row>
+    <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="7">
+        <v>40</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2000</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="7">
+        <v>80</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3594,7 +5454,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>217</v>
+        <v>277</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3650,13 +5510,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -3665,18 +5525,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>219</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -3692,21 +5552,21 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>222</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>223</v>
+        <v>283</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>224</v>
+        <v>284</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>224</v>
+        <v>284</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>195</v>
+        <v>242</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
@@ -3715,41 +5575,41 @@
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>225</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>226</v>
+        <v>286</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>227</v>
+        <v>287</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>228</v>
+        <v>288</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>229</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -3757,24 +5617,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>233</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>235</v>
+        <v>295</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -3782,24 +5642,24 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
       <c r="G9" s="7" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>236</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>237</v>
+        <v>297</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>238</v>
+        <v>298</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>238</v>
+        <v>298</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>73</v>
@@ -3811,30 +5671,30 @@
         <v>25</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>242</v>
+        <v>302</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="8"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>243</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3842,10 +5702,10 @@
         <v>56</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>213</v>
+        <v>260</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>59</v>
@@ -3887,7 +5747,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>304</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3943,13 +5803,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -3958,21 +5818,21 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>246</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>247</v>
+        <v>307</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>248</v>
+        <v>308</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>248</v>
+        <v>308</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>249</v>
+        <v>309</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8" t="s">
@@ -3983,18 +5843,18 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>250</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
@@ -4004,24 +5864,24 @@
         <v>21</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>253</v>
+        <v>313</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>254</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>42</v>
@@ -4037,18 +5897,18 @@
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>257</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>258</v>
+        <v>318</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>259</v>
+        <v>319</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>38</v>
@@ -4060,18 +5920,18 @@
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -4079,24 +5939,24 @@
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
       <c r="G9" s="7" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>261</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>262</v>
+        <v>322</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>73</v>
@@ -4110,18 +5970,18 @@
         <v>9</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>264</v>
+        <v>324</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>265</v>
+        <v>325</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>266</v>
+        <v>326</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -4129,18 +5989,18 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="9" t="s">
-        <v>267</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>268</v>
+        <v>328</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>269</v>
+        <v>329</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>266</v>
+        <v>326</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -4148,18 +6008,18 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="9" t="s">
-        <v>270</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>271</v>
+        <v>331</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>266</v>
+        <v>326</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -4167,76 +6027,76 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>273</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>274</v>
+        <v>334</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="8"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>275</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>276</v>
+        <v>336</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>277</v>
+        <v>337</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="8"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>278</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>281</v>
+        <v>341</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>282</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -4264,7 +6124,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4275,7 +6135,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -4320,10 +6180,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>20</v>
@@ -4339,21 +6199,21 @@
         <v>9</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>286</v>
+        <v>346</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>287</v>
+        <v>347</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>287</v>
+        <v>347</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -4362,18 +6222,18 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>288</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>289</v>
+        <v>349</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
@@ -4381,27 +6241,27 @@
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="7" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>291</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>292</v>
+        <v>352</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
@@ -4410,18 +6270,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>294</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>295</v>
+        <v>355</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>73</v>
@@ -4433,18 +6293,18 @@
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>73</v>
@@ -4462,10 +6322,10 @@
         <v>27</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -4473,7 +6333,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>25</v>
@@ -4482,13 +6342,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>301</v>
+        <v>361</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>38</v>
@@ -4503,13 +6363,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>38</v>
@@ -4521,18 +6381,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>307</v>
+        <v>367</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>308</v>
+        <v>368</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>42</v>
@@ -4541,10 +6401,10 @@
       <c r="F13" s="8"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>309</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -4552,6 +6412,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/項目定義書.xlsx
+++ b/docs/項目定義書.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="477">
   <si>
     <t>項目定義書　－ 取引先オブジェクト（Account）</t>
   </si>
@@ -294,13 +294,16 @@
     <t>CustomerCategory__c</t>
   </si>
   <si>
-    <t>法人区分</t>
-  </si>
-  <si>
-    <t>法人区分（カスタム）</t>
-  </si>
-  <si>
-    <t>オフィス/飲食店・カフェ</t>
+    <t>取引先区分</t>
+  </si>
+  <si>
+    <t>取引先区分（カスタム）</t>
+  </si>
+  <si>
+    <t>オフィス/飲食店・カフェ/自社店舗</t>
+  </si>
+  <si>
+    <t>カスタム項目（表示ラベルを 法人区分 から変更）。自社店舗＝三日月珈琲の各店舗の取引先（6店舗＋オンラインショップ）</t>
   </si>
   <si>
     <t>NameKey__c</t>
@@ -339,7 +342,7 @@
     <t>参照（Account）</t>
   </si>
   <si>
-    <t>取引先オブジェクトへの参照</t>
+    <t>個人のお客様（会員）は、フロー「取引先責任者：店舗の取引先に紐づけ」が、よく行く店舗の取引先（自社店舗）に紐づける。法人の担当者は動かさない</t>
   </si>
   <si>
     <t>LastName</t>
@@ -1110,6 +1113,24 @@
     <t>リピートなら1。レポートのリピート率の計算に使う</t>
   </si>
   <si>
+    <t>POSSale__c</t>
+  </si>
+  <si>
+    <t>POS売上明細</t>
+  </si>
+  <si>
+    <t>参照（POSSale__c）</t>
+  </si>
+  <si>
+    <t>このポイントのもとになった売上</t>
+  </si>
+  <si>
+    <t>Contact__c</t>
+  </si>
+  <si>
+    <t>フロー「ポイント履歴：会員の自動設定」がポイントカードの会員を入れる。取引先責任者の画面の関連リスト「ポイント履歴」に出る</t>
+  </si>
+  <si>
     <t>項目定義書　－ キャンペーンオブジェクト（Campaign）</t>
   </si>
   <si>
@@ -1384,6 +1405,9 @@
   </si>
   <si>
     <t>会員以外も含めたキャンペーン効果の集計に使う</t>
+  </si>
+  <si>
+    <t>ポイントカードがあれば、フロー「POS売上明細：会員の自動設定」がカードの会員を入れる。取引先責任者の画面の関連リスト「売上履歴」に出る</t>
   </si>
   <si>
     <t>項目定義書　－ キャンペーンメンバーオブジェクト（CampaignMember）</t>
@@ -2507,18 +2531,18 @@
         <v>25</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>20</v>
@@ -2529,10 +2553,10 @@
       <c r="F22" s="8"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2559,7 +2583,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2615,10 +2639,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>20</v>
@@ -2634,18 +2658,18 @@
         <v>9</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2659,18 +2683,18 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>20</v>
@@ -2684,18 +2708,18 @@
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -2703,24 +2727,24 @@
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -2728,24 +2752,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>20</v>
@@ -2764,13 +2788,13 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -2778,7 +2802,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>25</v>
@@ -2789,16 +2813,16 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="8"/>
@@ -2807,7 +2831,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2815,10 +2839,10 @@
         <v>61</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>64</v>
@@ -2832,18 +2856,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>38</v>
@@ -2855,7 +2879,7 @@
         <v>25</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -2869,7 +2893,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -2883,7 +2907,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2939,13 +2963,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -2954,18 +2978,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -2979,21 +3003,21 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
@@ -3008,10 +3032,10 @@
         <v>79</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -3025,18 +3049,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>20</v>
@@ -3053,16 +3077,16 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="8"/>
@@ -3071,18 +3095,18 @@
         <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>20</v>
@@ -3096,18 +3120,18 @@
         <v>25</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
@@ -3121,18 +3145,18 @@
         <v>25</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>20</v>
@@ -3146,18 +3170,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>42</v>
@@ -3174,13 +3198,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>38</v>
@@ -3195,13 +3219,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>38</v>
@@ -3216,13 +3240,13 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>29</v>
@@ -3230,7 +3254,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="7" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>25</v>
@@ -3239,16 +3263,16 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="8"/>
@@ -3257,21 +3281,21 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="8"/>
@@ -3280,7 +3304,30 @@
         <v>25</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>452</v>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -3308,7 +3355,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3361,16 +3408,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8" t="s">
@@ -3384,16 +3431,16 @@
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -3402,18 +3449,18 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
@@ -3421,24 +3468,24 @@
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="7" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -3452,26 +3499,26 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
@@ -3482,13 +3529,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>73</v>
@@ -3528,7 +3575,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3581,10 +3628,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -3601,7 +3648,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3609,35 +3656,33 @@
         <v>13</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E5" s="7"/>
-      <c r="F5" s="8" t="s">
-        <v>21</v>
-      </c>
+      <c r="F5" s="8"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
@@ -3656,13 +3701,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -3679,13 +3724,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>20</v>
@@ -3702,13 +3747,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>20</v>
@@ -3725,16 +3770,16 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E10" s="10">
         <v>80</v>
@@ -3754,7 +3799,7 @@
         <v>48</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>50</v>
@@ -3771,13 +3816,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>50</v>
@@ -3794,13 +3839,13 @@
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>45</v>
@@ -3818,7 +3863,7 @@
         <v>56</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="21" t="s">
         <v>58</v>
@@ -3839,10 +3884,10 @@
         <v>79</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>29</v>
@@ -3856,18 +3901,18 @@
         <v>25</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>73</v>
@@ -3884,13 +3929,13 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>29</v>
@@ -3898,7 +3943,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="8"/>
       <c r="G17" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>25</v>
@@ -3909,13 +3954,13 @@
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>20</v>
@@ -3929,18 +3974,18 @@
         <v>25</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>20</v>
@@ -3959,13 +4004,13 @@
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>20</v>
@@ -3979,18 +4024,18 @@
         <v>25</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>42</v>
@@ -4004,18 +4049,18 @@
         <v>25</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>73</v>
@@ -4079,7 +4124,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4132,10 +4177,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4152,7 +4197,7 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4160,10 +4205,10 @@
         <v>18</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -4179,7 +4224,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4190,10 +4235,10 @@
         <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="20" t="s">
@@ -4207,13 +4252,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -4223,24 +4268,24 @@
         <v>21</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>73</v>
@@ -4257,13 +4302,13 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>38</v>
@@ -4278,36 +4323,36 @@
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="11"/>
       <c r="G10" s="10"/>
       <c r="H10" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -4315,7 +4360,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="13"/>
       <c r="G11" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>25</v>
@@ -4330,7 +4375,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>64</v>
@@ -4350,7 +4395,7 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>58</v>
@@ -4368,13 +4413,13 @@
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>20</v>
@@ -4393,13 +4438,13 @@
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D15" s="17" t="s">
         <v>29</v>
@@ -4407,13 +4452,13 @@
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
       <c r="G15" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4421,10 +4466,10 @@
         <v>79</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>29</v>
@@ -4438,18 +4483,18 @@
         <v>25</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>38</v>
@@ -4461,7 +4506,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4469,10 +4514,10 @@
         <v>27</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>29</v>
@@ -4480,27 +4525,27 @@
       <c r="E18" s="7"/>
       <c r="F18" s="8"/>
       <c r="G18" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
@@ -4509,7 +4554,7 @@
         <v>25</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -4539,13 +4584,13 @@
     </row>
     <row r="21" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>73</v>
@@ -4562,13 +4607,13 @@
     </row>
     <row r="22" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>20</v>
@@ -4582,21 +4627,21 @@
         <v>25</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="8"/>
@@ -4605,18 +4650,18 @@
         <v>25</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>29</v>
@@ -4624,13 +4669,13 @@
       <c r="E24" s="7"/>
       <c r="F24" s="8"/>
       <c r="G24" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4657,7 +4702,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4710,10 +4755,10 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>15</v>
@@ -4730,18 +4775,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -4760,13 +4805,13 @@
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>20</v>
@@ -4783,13 +4828,13 @@
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>20</v>
@@ -4808,13 +4853,13 @@
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>20</v>
@@ -4831,16 +4876,16 @@
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E9" s="7">
         <v>80</v>
@@ -4877,13 +4922,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>29</v>
@@ -4893,7 +4938,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>9</v>
@@ -4902,13 +4947,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>29</v>
@@ -4916,24 +4961,24 @@
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
       <c r="G12" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>25</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>29</v>
@@ -4941,7 +4986,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="13"/>
       <c r="G13" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>25</v>
@@ -4956,7 +5001,7 @@
         <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>64</v>
@@ -4976,7 +5021,7 @@
         <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>58</v>
@@ -4994,16 +5039,16 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="25"/>
@@ -5012,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="I16" s="26" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5037,7 +5082,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5062,18 +5107,18 @@
         <v>25</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>73</v>
@@ -5085,18 +5130,18 @@
         <v>25</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>20</v>
@@ -5107,10 +5152,10 @@
       <c r="F20" s="8"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -5137,7 +5182,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5193,10 +5238,10 @@
         <v>79</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>29</v>
@@ -5210,7 +5255,7 @@
         <v>25</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -5238,7 +5283,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5291,16 +5336,16 @@
     </row>
     <row r="4" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="7">
         <v>30</v>
@@ -5311,21 +5356,21 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -5334,7 +5379,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5342,22 +5387,22 @@
         <v>13</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5365,10 +5410,10 @@
         <v>79</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
@@ -5382,7 +5427,7 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5390,10 +5435,10 @@
         <v>27</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -5401,24 +5446,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -5428,24 +5473,24 @@
         <v>21</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -5455,24 +5500,24 @@
         <v>21</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
@@ -5495,7 +5540,7 @@
         <v>62</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>64</v>
@@ -5515,13 +5560,13 @@
         <v>56</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="8" t="s">
@@ -5532,18 +5577,18 @@
         <v>9</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>73</v>
@@ -5555,7 +5600,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5563,10 +5608,10 @@
         <v>84</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>20</v>
@@ -5585,13 +5630,13 @@
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>64</v>
@@ -5610,13 +5655,13 @@
     </row>
     <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>20</v>
@@ -5630,7 +5675,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -5658,7 +5703,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5714,13 +5759,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -5729,18 +5774,18 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>20</v>
@@ -5756,21 +5801,21 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
@@ -5779,41 +5824,41 @@
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>29</v>
@@ -5821,24 +5866,24 @@
       <c r="E8" s="7"/>
       <c r="F8" s="8"/>
       <c r="G8" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -5852,18 +5897,18 @@
         <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>73</v>
@@ -5875,30 +5920,30 @@
         <v>25</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="8"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -5906,10 +5951,10 @@
         <v>56</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>59</v>
@@ -5937,7 +5982,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="22.69921875" customWidth="1"/>
@@ -5951,7 +5996,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6007,13 +6052,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
@@ -6022,21 +6067,21 @@
         <v>16</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8" t="s">
@@ -6047,18 +6092,18 @@
         <v>9</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
@@ -6068,24 +6113,24 @@
         <v>21</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>42</v>
@@ -6101,18 +6146,18 @@
         <v>9</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>38</v>
@@ -6124,7 +6169,7 @@
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6132,10 +6177,10 @@
         <v>79</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>29</v>
@@ -6149,18 +6194,18 @@
         <v>25</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>73</v>
@@ -6174,18 +6219,18 @@
         <v>9</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -6193,18 +6238,18 @@
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -6212,18 +6257,18 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -6231,76 +6276,122 @@
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
       <c r="I13" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="8"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="8"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="8"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="17" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
@@ -6328,7 +6419,7 @@
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6384,10 +6475,10 @@
         <v>18</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>20</v>
@@ -6403,21 +6494,21 @@
         <v>9</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
@@ -6426,7 +6517,7 @@
         <v>25</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -6434,10 +6525,10 @@
         <v>79</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>29</v>
@@ -6451,21 +6542,21 @@
         <v>25</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
@@ -6474,18 +6565,18 @@
         <v>25</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>73</v>
@@ -6497,18 +6588,18 @@
         <v>25</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>73</v>
@@ -6526,10 +6617,10 @@
         <v>27</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>29</v>
@@ -6537,7 +6628,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="8"/>
       <c r="G10" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>25</v>
@@ -6546,13 +6637,13 @@
     </row>
     <row r="11" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>38</v>
@@ -6567,13 +6658,13 @@
     </row>
     <row r="12" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>38</v>
@@ -6585,18 +6676,18 @@
         <v>25</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" ht="34.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>42</v>
@@ -6605,10 +6696,10 @@
       <c r="F13" s="8"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
